--- a/Shiny/Datos limpios/pricing_semanal_soja_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_soja_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -2073,16 +2073,16 @@
         <v>45922</v>
       </c>
       <c r="D40">
-        <v>3943194.35</v>
+        <v>3942409.22</v>
       </c>
       <c r="E40">
-        <v>75248.37</v>
+        <v>75322.2</v>
       </c>
       <c r="F40">
-        <v>39985.77</v>
+        <v>40620.9</v>
       </c>
       <c r="G40">
-        <v>3978456.95</v>
+        <v>3977110.52</v>
       </c>
       <c r="H40">
         <v>640164.45</v>
@@ -2097,7 +2097,7 @@
         <v>638882.0199999999</v>
       </c>
       <c r="L40">
-        <v>4617338.97</v>
+        <v>4615992.54</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2116,16 +2116,16 @@
         <v>45929</v>
       </c>
       <c r="D41">
-        <v>1864499.86</v>
+        <v>1863376.06</v>
       </c>
       <c r="E41">
-        <v>13593.59</v>
+        <v>14566.94</v>
       </c>
       <c r="F41">
         <v>40281.64</v>
       </c>
       <c r="G41">
-        <v>1837811.81</v>
+        <v>1837661.36</v>
       </c>
       <c r="H41">
         <v>461513.12</v>
@@ -2140,7 +2140,7 @@
         <v>460502.49</v>
       </c>
       <c r="L41">
-        <v>2298314.3</v>
+        <v>2298163.85</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2159,16 +2159,16 @@
         <v>45936</v>
       </c>
       <c r="D42">
-        <v>927140.8</v>
+        <v>927080.8</v>
       </c>
       <c r="E42">
         <v>14720.14</v>
       </c>
       <c r="F42">
-        <v>25249.67</v>
+        <v>25309.67</v>
       </c>
       <c r="G42">
-        <v>916611.27</v>
+        <v>916491.27</v>
       </c>
       <c r="H42">
         <v>275639.86</v>
@@ -2183,7 +2183,7 @@
         <v>252961.98</v>
       </c>
       <c r="L42">
-        <v>1169573.25</v>
+        <v>1169453.25</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2288,33 +2288,162 @@
         <v>45957</v>
       </c>
       <c r="D45">
-        <v>2677.84</v>
+        <v>275694.76</v>
       </c>
       <c r="E45">
+        <v>2521.58</v>
+      </c>
+      <c r="F45">
+        <v>11189.14</v>
+      </c>
+      <c r="G45">
+        <v>267027.2</v>
+      </c>
+      <c r="H45">
+        <v>86572.41</v>
+      </c>
+      <c r="I45">
+        <v>80</v>
+      </c>
+      <c r="J45">
+        <v>30</v>
+      </c>
+      <c r="K45">
+        <v>86622.41</v>
+      </c>
+      <c r="L45">
+        <v>353649.61</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D46">
+        <v>415929.3</v>
+      </c>
+      <c r="E46">
+        <v>15637.98</v>
+      </c>
+      <c r="F46">
+        <v>8841.51</v>
+      </c>
+      <c r="G46">
+        <v>422725.77</v>
+      </c>
+      <c r="H46">
+        <v>48483.55</v>
+      </c>
+      <c r="I46">
+        <v>2200</v>
+      </c>
+      <c r="J46">
+        <v>132.8</v>
+      </c>
+      <c r="K46">
+        <v>50550.75</v>
+      </c>
+      <c r="L46">
+        <v>473276.52</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D47">
+        <v>272004.97</v>
+      </c>
+      <c r="E47">
+        <v>7218.83</v>
+      </c>
+      <c r="F47">
+        <v>7370.28</v>
+      </c>
+      <c r="G47">
+        <v>271853.52</v>
+      </c>
+      <c r="H47">
+        <v>61996.76</v>
+      </c>
+      <c r="I47">
         <v>0</v>
       </c>
-      <c r="F45">
+      <c r="J47">
+        <v>311.65</v>
+      </c>
+      <c r="K47">
+        <v>61685.11</v>
+      </c>
+      <c r="L47">
+        <v>333538.6299999999</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D48">
+        <v>259822.1</v>
+      </c>
+      <c r="E48">
+        <v>2967.96</v>
+      </c>
+      <c r="F48">
+        <v>400.52</v>
+      </c>
+      <c r="G48">
+        <v>262389.54</v>
+      </c>
+      <c r="H48">
+        <v>89459.39999999999</v>
+      </c>
+      <c r="I48">
         <v>0</v>
       </c>
-      <c r="G45">
-        <v>2677.84</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>2677.84</v>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="J48">
+        <v>420</v>
+      </c>
+      <c r="K48">
+        <v>89039.39999999999</v>
+      </c>
+      <c r="L48">
+        <v>351428.9399999999</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>SOJA</t>
         </is>
